--- a/file_upload_forms/020_licence_renewal_form--file_upload_forms.xlsx
+++ b/file_upload_forms/020_licence_renewal_form--file_upload_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -437,13 +437,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="17" customWidth="1" min="1" max="1"/>
-    <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="31" customWidth="1" min="2" max="2"/>
+    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
@@ -515,69 +515,81 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>select_one</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>licence_renewal_form</t>
+          <t>current_license_type</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>licence_renewal_form</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
+          <t>What is your current license type?</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Please select your current license type</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>select_multiple</t>
+          <t>text</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>file_uploads</t>
+          <t>name_on_license</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>file_uploads</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr"/>
+          <t>What is your name as it appears on the license?</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Please enter your name exactly as it appears on your license</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>text</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>licence_renewal_form</t>
+          <t>date_of_birth</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>licence_renewal_form</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr"/>
+          <t>What is your date of birth?</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Please enter your date of birth in the format mm/dd/yyyy</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -589,18 +601,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>file_uploads</t>
+          <t>current_address</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>file_uploads</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr"/>
+          <t>What is your current address?</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Please enter your current address</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
     </row>
@@ -612,16 +628,209 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>licence_renewal_form</t>
+          <t>outstanding_traffic_offenses</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>licence_renewal_form</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr"/>
+          <t>Do you have any outstanding traffic offenses?</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Please select one of the options</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>years_held_license</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>How long have you held this license?</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Please enter the number of years</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>last_license_renewal_date</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>When did you last renew your license?</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Please enter the date of last license renewal in the format mm/dd/yyyy</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>contact_number</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>What is your contact number?</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Please enter your contact number</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>address_or_employment_changes</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Do you have any new addresses or employment changes?</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Please enter details of changes</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>select_one</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>traffic_accident_involvement</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Have you been involved in any traffic accidents since your last license renewal?</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Please select one of the options</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>license_renewal_date</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>What is your license renewal date (mm/dd/yyyy)?</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Please enter your license renewal date in the format mm/dd/yyyy</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>text</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>additional_comments</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Additional comments</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Please add any additional comments</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
         <is>
           <t>no</t>
         </is>
@@ -638,12 +847,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C5"/>
+  <dimension ref="A1:C8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="30" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="7" customWidth="1" min="3" max="3"/>
+    <col width="38" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -666,68 +875,119 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>file_uploads_choices</t>
+          <t>current_license_type_choices</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>driver's_license</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Driver's License</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>file_uploads_choices</t>
+          <t>current_license_type_choices</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>vehicle_license</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Vehicle License</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>licence_renewal_form_choices</t>
+          <t>current_license_type_choices</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>licence_renewal_form_choices</t>
+          <t>outstanding_traffic_offenses_choices</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>outstanding_traffic_offenses_choices</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>traffic_accident_involvement_choices</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>true</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>True</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>traffic_accident_involvement_choices</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>false</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>False</t>
         </is>
       </c>
     </row>
